--- a/diseases/d110/2000-2004.xlsx
+++ b/diseases/d110/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>5</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.09659593043277004</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>18</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>6.399317406143345</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>15</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.3340112276760813</v>
       </c>
@@ -2397,9 +2388,6 @@
       <c r="O11" t="n">
         <v>5</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.09659593043277004</v>
       </c>
@@ -2941,9 +2929,6 @@
       <c r="O14" t="n">
         <v>7</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.1558719062488379</v>
       </c>
@@ -3485,9 +3470,6 @@
       <c r="O17" t="n">
         <v>10</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.1931918608655401</v>
       </c>
@@ -4029,9 +4011,6 @@
       <c r="O20" t="n">
         <v>3</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.06680224553521626</v>
       </c>
@@ -4573,9 +4552,6 @@
       <c r="O23" t="n">
         <v>4</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.07727674434621605</v>
       </c>
@@ -5117,9 +5093,6 @@
       <c r="O26" t="n">
         <v>5</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.1113370758920271</v>
       </c>
@@ -5661,9 +5634,6 @@
       <c r="O29" t="n">
         <v>2</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -6205,9 +6175,6 @@
       <c r="O32" t="n">
         <v>2</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.04453483035681084</v>
       </c>
@@ -6749,9 +6716,6 @@
       <c r="O35" t="n">
         <v>3</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.05795755825966203</v>
       </c>
@@ -7293,9 +7257,6 @@
       <c r="O38" t="n">
         <v>7</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.1558719062488379</v>
       </c>
@@ -7837,9 +7798,6 @@
       <c r="O41" t="n">
         <v>3</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.05795755825966203</v>
       </c>
@@ -8381,9 +8339,6 @@
       <c r="O44" t="n">
         <v>10</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.2226741517840542</v>
       </c>
@@ -8925,9 +8880,6 @@
       <c r="O47" t="n">
         <v>3</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.05795755825966203</v>
       </c>
@@ -9469,9 +9421,6 @@
       <c r="O50" t="n">
         <v>2</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.04453483035681084</v>
       </c>
@@ -10013,9 +9962,6 @@
       <c r="O53" t="n">
         <v>2</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -10557,9 +10503,6 @@
       <c r="O56" t="n">
         <v>13</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.2894763973192704</v>
       </c>
@@ -11101,9 +11044,6 @@
       <c r="O59" t="n">
         <v>3</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.05795755825966203</v>
       </c>
@@ -11645,9 +11585,6 @@
       <c r="O62" t="n">
         <v>6</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.1336044910704325</v>
       </c>
@@ -12189,9 +12126,6 @@
       <c r="O65" t="n">
         <v>4</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.07727674434621605</v>
       </c>
@@ -12733,9 +12667,6 @@
       <c r="O68" t="n">
         <v>5</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.1113370758920271</v>
       </c>
@@ -13277,9 +13208,6 @@
       <c r="O71" t="n">
         <v>4</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.07727674434621605</v>
       </c>
@@ -13821,9 +13749,6 @@
       <c r="O74" t="n">
         <v>8</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.1781393214272433</v>
       </c>
@@ -14365,9 +14290,6 @@
       <c r="O77" t="n">
         <v>5</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.09637679162046203</v>
       </c>
@@ -14909,9 +14831,6 @@
       <c r="O80" t="n">
         <v>18</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>6.314626253058647</v>
       </c>
@@ -15305,9 +15224,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -15453,9 +15369,6 @@
       <c r="O83" t="n">
         <v>12</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.2658598116782024</v>
       </c>
@@ -15997,9 +15910,6 @@
       <c r="O86" t="n">
         <v>6</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.1156521499445544</v>
       </c>
@@ -16541,9 +16451,6 @@
       <c r="O89" t="n">
         <v>3</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.006377080873374387</v>
       </c>
@@ -16689,9 +16596,6 @@
       <c r="O90" t="n">
         <v>5</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.1107749215325843</v>
       </c>
@@ -17233,9 +17137,6 @@
       <c r="O93" t="n">
         <v>4</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.07710143329636962</v>
       </c>
@@ -17777,9 +17678,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -17925,9 +17823,6 @@
       <c r="O97" t="n">
         <v>10</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.2215498430651687</v>
       </c>
@@ -18469,9 +18364,6 @@
       <c r="O100" t="n">
         <v>7</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.1349275082686468</v>
       </c>
@@ -19013,9 +18905,6 @@
       <c r="O103" t="n">
         <v>2</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.004251387248916258</v>
       </c>
@@ -19161,9 +19050,6 @@
       <c r="O104" t="n">
         <v>8</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.1772398744521349</v>
       </c>
@@ -19705,9 +19591,6 @@
       <c r="O107" t="n">
         <v>3</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -20249,9 +20132,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -20397,9 +20277,6 @@
       <c r="O111" t="n">
         <v>7</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.1550848901456181</v>
       </c>
@@ -20941,9 +20818,6 @@
       <c r="O114" t="n">
         <v>6</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.1156521499445544</v>
       </c>
@@ -21485,9 +21359,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -21633,9 +21504,6 @@
       <c r="O118" t="n">
         <v>4</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.08861993722606747</v>
       </c>
@@ -22177,9 +22045,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -22721,9 +22586,6 @@
       <c r="O124" t="n">
         <v>1</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -22869,9 +22731,6 @@
       <c r="O125" t="n">
         <v>4</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.08861993722606747</v>
       </c>
@@ -23413,9 +23272,6 @@
       <c r="O128" t="n">
         <v>1</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -23957,9 +23813,6 @@
       <c r="O131" t="n">
         <v>3</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.006377080873374387</v>
       </c>
@@ -24105,9 +23958,6 @@
       <c r="O132" t="n">
         <v>9</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.1993948587586518</v>
       </c>
@@ -24649,9 +24499,6 @@
       <c r="O135" t="n">
         <v>3</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -25193,9 +25040,6 @@
       <c r="O138" t="n">
         <v>1</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -25341,9 +25185,6 @@
       <c r="O139" t="n">
         <v>6</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.1329299058391012</v>
       </c>
@@ -25885,9 +25726,6 @@
       <c r="O142" t="n">
         <v>5</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.09637679162046203</v>
       </c>
@@ -26429,9 +26267,6 @@
       <c r="O145" t="n">
         <v>1</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -26577,9 +26412,6 @@
       <c r="O146" t="n">
         <v>8</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.1772398744521349</v>
       </c>
@@ -27121,9 +26953,6 @@
       <c r="O149" t="n">
         <v>4</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.07710143329636962</v>
       </c>
@@ -27665,9 +27494,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -27813,9 +27639,6 @@
       <c r="O153" t="n">
         <v>3</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.0664649529195506</v>
       </c>
@@ -28357,9 +28180,6 @@
       <c r="O156" t="n">
         <v>3</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -28901,9 +28721,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -29049,9 +28866,6 @@
       <c r="O160" t="n">
         <v>2</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -29593,9 +29407,6 @@
       <c r="O163" t="n">
         <v>3</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.05768625063599091</v>
       </c>
@@ -30137,9 +29948,6 @@
       <c r="O166" t="n">
         <v>15</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>5.215450249820067</v>
       </c>
@@ -30533,9 +30341,6 @@
       <c r="O168" t="n">
         <v>2</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.004228408433091266</v>
       </c>
@@ -30681,9 +30486,6 @@
       <c r="O169" t="n">
         <v>5</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.1101803564290458</v>
       </c>
@@ -31225,9 +31027,6 @@
       <c r="O172" t="n">
         <v>2</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -31769,9 +31568,6 @@
       <c r="O175" t="n">
         <v>1</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -31917,9 +31713,6 @@
       <c r="O176" t="n">
         <v>9</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.1983246415722825</v>
       </c>
@@ -32461,9 +32254,6 @@
       <c r="O179" t="n">
         <v>3</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.05768625063599091</v>
       </c>
@@ -33005,9 +32795,6 @@
       <c r="O182" t="n">
         <v>1</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -33153,9 +32940,6 @@
       <c r="O183" t="n">
         <v>3</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.0661082138574275</v>
       </c>
@@ -33697,9 +33481,6 @@
       <c r="O186" t="n">
         <v>3</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.05768625063599091</v>
       </c>
@@ -34241,9 +34022,6 @@
       <c r="O189" t="n">
         <v>6</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.0126852252992738</v>
       </c>
@@ -34389,9 +34167,6 @@
       <c r="O190" t="n">
         <v>2</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -34933,9 +34708,6 @@
       <c r="O193" t="n">
         <v>5</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.09614375105998485</v>
       </c>
@@ -35477,9 +35249,6 @@
       <c r="O196" t="n">
         <v>4</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.008456816866182533</v>
       </c>
@@ -35625,9 +35394,6 @@
       <c r="O197" t="n">
         <v>9</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.1983246415722825</v>
       </c>
@@ -36169,9 +35935,6 @@
       <c r="O200" t="n">
         <v>5</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.09614375105998485</v>
       </c>
@@ -36713,9 +36476,6 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
@@ -36861,9 +36621,6 @@
       <c r="O204" t="n">
         <v>5</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.1101803564290458</v>
       </c>
@@ -37405,9 +37162,6 @@
       <c r="O207" t="n">
         <v>4</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.07691500084798789</v>
       </c>
@@ -37949,9 +37703,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -38097,9 +37848,6 @@
       <c r="O211" t="n">
         <v>2</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -38641,9 +38389,6 @@
       <c r="O214" t="n">
         <v>1</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -39185,9 +38930,6 @@
       <c r="O217" t="n">
         <v>1</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -39333,9 +39075,6 @@
       <c r="O218" t="n">
         <v>3</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.0661082138574275</v>
       </c>
@@ -39877,9 +39616,6 @@
       <c r="O221" t="n">
         <v>3</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.05768625063599091</v>
       </c>
@@ -40421,9 +40157,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -40569,9 +40302,6 @@
       <c r="O225" t="n">
         <v>4</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.08814428514323666</v>
       </c>
@@ -41113,9 +40843,6 @@
       <c r="O228" t="n">
         <v>7</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.1346012514839788</v>
       </c>
@@ -41657,9 +41384,6 @@
       <c r="O231" t="n">
         <v>1</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -41805,9 +41529,6 @@
       <c r="O232" t="n">
         <v>3</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.0661082138574275</v>
       </c>
@@ -42349,9 +42070,6 @@
       <c r="O235" t="n">
         <v>5</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.09614375105998485</v>
       </c>
@@ -42893,9 +42611,6 @@
       <c r="O238" t="n">
         <v>3</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.006342612649636899</v>
       </c>
@@ -43041,9 +42756,6 @@
       <c r="O239" t="n">
         <v>1</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -43585,9 +43297,6 @@
       <c r="O242" t="n">
         <v>7</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0.1346012514839788</v>
       </c>
@@ -44129,9 +43838,6 @@
       <c r="O245" t="n">
         <v>8</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.01691363373236507</v>
       </c>
@@ -44277,9 +43983,6 @@
       <c r="O246" t="n">
         <v>5</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0.1101803564290458</v>
       </c>
@@ -44821,9 +44524,6 @@
       <c r="O249" t="n">
         <v>4</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0.07673191117130304</v>
       </c>
@@ -45365,9 +45065,6 @@
       <c r="O252" t="n">
         <v>8</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>2.762383246145612</v>
       </c>
@@ -45761,9 +45458,6 @@
       <c r="O254" t="n">
         <v>9</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.01894172159476542</v>
       </c>
@@ -45909,9 +45603,6 @@
       <c r="O255" t="n">
         <v>4</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.08762957401730553</v>
       </c>
@@ -46601,9 +46292,6 @@
       <c r="O259" t="n">
         <v>5</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0.09591488896412878</v>
       </c>
@@ -47145,9 +46833,6 @@
       <c r="O262" t="n">
         <v>3</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -47293,9 +46978,6 @@
       <c r="O263" t="n">
         <v>3</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0.06572218051297914</v>
       </c>
@@ -47985,9 +47667,6 @@
       <c r="O267" t="n">
         <v>2</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -48529,9 +48208,6 @@
       <c r="O270" t="n">
         <v>3</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -48677,9 +48353,6 @@
       <c r="O271" t="n">
         <v>5</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0.1095369675216319</v>
       </c>
@@ -49369,9 +49042,6 @@
       <c r="O275" t="n">
         <v>2</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -49913,9 +49583,6 @@
       <c r="O278" t="n">
         <v>5</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.01052317866375857</v>
       </c>
@@ -50061,9 +49728,6 @@
       <c r="O279" t="n">
         <v>5</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0.1095369675216319</v>
       </c>
@@ -50753,9 +50417,6 @@
       <c r="O283" t="n">
         <v>6</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0.1150978667569545</v>
       </c>
@@ -51297,9 +50958,6 @@
       <c r="O286" t="n">
         <v>5</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0.01052317866375857</v>
       </c>
@@ -51445,9 +51103,6 @@
       <c r="O287" t="n">
         <v>4</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0.08762957401730553</v>
       </c>
@@ -52137,9 +51792,6 @@
       <c r="O291" t="n">
         <v>0</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0</v>
       </c>
@@ -52681,9 +52333,6 @@
       <c r="O294" t="n">
         <v>3</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -52829,9 +52478,6 @@
       <c r="O295" t="n">
         <v>2</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -53521,9 +53167,6 @@
       <c r="O299" t="n">
         <v>4</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0.07673191117130304</v>
       </c>
@@ -54065,9 +53708,6 @@
       <c r="O302" t="n">
         <v>2</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0.004209271465503426</v>
       </c>
@@ -54213,9 +53853,6 @@
       <c r="O303" t="n">
         <v>2</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -54905,9 +54542,6 @@
       <c r="O307" t="n">
         <v>2</v>
       </c>
-      <c r="Q307" t="n">
-        <v>0</v>
-      </c>
       <c r="R307" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -55449,9 +55083,6 @@
       <c r="O310" t="n">
         <v>3</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="R310" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -55597,9 +55228,6 @@
       <c r="O311" t="n">
         <v>2</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -56289,9 +55917,6 @@
       <c r="O315" t="n">
         <v>6</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0.1150978667569545</v>
       </c>
@@ -56833,9 +56458,6 @@
       <c r="O318" t="n">
         <v>1</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -56981,9 +56603,6 @@
       <c r="O319" t="n">
         <v>4</v>
       </c>
-      <c r="Q319" t="n">
-        <v>0</v>
-      </c>
       <c r="R319" t="n">
         <v>0.08762957401730553</v>
       </c>
@@ -57673,9 +57292,6 @@
       <c r="O323" t="n">
         <v>2</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -58217,9 +57833,6 @@
       <c r="O326" t="n">
         <v>1</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -58365,9 +57978,6 @@
       <c r="O327" t="n">
         <v>8</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0.1752591480346111</v>
       </c>
@@ -59057,9 +58667,6 @@
       <c r="O331" t="n">
         <v>1</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -59601,9 +59208,6 @@
       <c r="O334" t="n">
         <v>1</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -59749,9 +59353,6 @@
       <c r="O335" t="n">
         <v>5</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0.1095369675216319</v>
       </c>
@@ -60441,9 +60042,6 @@
       <c r="O339" t="n">
         <v>7</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0.1342808445497803</v>
       </c>
@@ -60985,9 +60583,6 @@
       <c r="O342" t="n">
         <v>2</v>
       </c>
-      <c r="Q342" t="n">
-        <v>0</v>
-      </c>
       <c r="R342" t="n">
         <v>0.004209271465503426</v>
       </c>
@@ -61133,9 +60728,6 @@
       <c r="O343" t="n">
         <v>4</v>
       </c>
-      <c r="Q343" t="n">
-        <v>0</v>
-      </c>
       <c r="R343" t="n">
         <v>0.08762957401730553</v>
       </c>
@@ -61825,9 +61417,6 @@
       <c r="O347" t="n">
         <v>1</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -62369,9 +61958,6 @@
       <c r="O350" t="n">
         <v>10</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>3.422682458923532</v>
       </c>
@@ -62765,9 +62351,6 @@
       <c r="O352" t="n">
         <v>2</v>
       </c>
-      <c r="Q352" t="n">
-        <v>0</v>
-      </c>
       <c r="R352" t="n">
         <v>0.004193129199294409</v>
       </c>
@@ -62913,9 +62496,6 @@
       <c r="O353" t="n">
         <v>7</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0.152447573007415</v>
       </c>
@@ -63605,9 +63185,6 @@
       <c r="O357" t="n">
         <v>4</v>
       </c>
-      <c r="Q357" t="n">
-        <v>0</v>
-      </c>
       <c r="R357" t="n">
         <v>0.07650892820937739</v>
       </c>
@@ -64149,9 +63726,6 @@
       <c r="O360" t="n">
         <v>1</v>
       </c>
-      <c r="Q360" t="n">
-        <v>0</v>
-      </c>
       <c r="R360" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -64297,9 +63871,6 @@
       <c r="O361" t="n">
         <v>1</v>
       </c>
-      <c r="Q361" t="n">
-        <v>0</v>
-      </c>
       <c r="R361" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -64989,9 +64560,6 @@
       <c r="O365" t="n">
         <v>3</v>
       </c>
-      <c r="Q365" t="n">
-        <v>0</v>
-      </c>
       <c r="R365" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -65533,9 +65101,6 @@
       <c r="O368" t="n">
         <v>1</v>
       </c>
-      <c r="Q368" t="n">
-        <v>0</v>
-      </c>
       <c r="R368" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -65681,9 +65246,6 @@
       <c r="O369" t="n">
         <v>1</v>
       </c>
-      <c r="Q369" t="n">
-        <v>0</v>
-      </c>
       <c r="R369" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -66373,9 +65935,6 @@
       <c r="O373" t="n">
         <v>4</v>
       </c>
-      <c r="Q373" t="n">
-        <v>0</v>
-      </c>
       <c r="R373" t="n">
         <v>0.07650892820937739</v>
       </c>
@@ -66917,9 +66476,6 @@
       <c r="O376" t="n">
         <v>0</v>
       </c>
-      <c r="Q376" t="n">
-        <v>0</v>
-      </c>
       <c r="R376" t="n">
         <v>0</v>
       </c>
@@ -67065,9 +66621,6 @@
       <c r="O377" t="n">
         <v>4</v>
       </c>
-      <c r="Q377" t="n">
-        <v>0</v>
-      </c>
       <c r="R377" t="n">
         <v>0.08711289886137998</v>
       </c>
@@ -67757,9 +67310,6 @@
       <c r="O381" t="n">
         <v>5</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0.09563616026172174</v>
       </c>
@@ -68301,9 +67851,6 @@
       <c r="O384" t="n">
         <v>0</v>
       </c>
-      <c r="Q384" t="n">
-        <v>0</v>
-      </c>
       <c r="R384" t="n">
         <v>0</v>
       </c>
@@ -68449,9 +67996,6 @@
       <c r="O385" t="n">
         <v>1</v>
       </c>
-      <c r="Q385" t="n">
-        <v>0</v>
-      </c>
       <c r="R385" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -69141,9 +68685,6 @@
       <c r="O389" t="n">
         <v>4</v>
       </c>
-      <c r="Q389" t="n">
-        <v>0</v>
-      </c>
       <c r="R389" t="n">
         <v>0.07650892820937739</v>
       </c>
@@ -69685,9 +69226,6 @@
       <c r="O392" t="n">
         <v>0</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>0</v>
       </c>
@@ -69833,9 +69371,6 @@
       <c r="O393" t="n">
         <v>5</v>
       </c>
-      <c r="Q393" t="n">
-        <v>0</v>
-      </c>
       <c r="R393" t="n">
         <v>0.108891123576725</v>
       </c>
@@ -70525,9 +70060,6 @@
       <c r="O397" t="n">
         <v>3</v>
       </c>
-      <c r="Q397" t="n">
-        <v>0</v>
-      </c>
       <c r="R397" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -71069,9 +70601,6 @@
       <c r="O400" t="n">
         <v>0</v>
       </c>
-      <c r="Q400" t="n">
-        <v>0</v>
-      </c>
       <c r="R400" t="n">
         <v>0</v>
       </c>
@@ -71217,9 +70746,6 @@
       <c r="O401" t="n">
         <v>4</v>
       </c>
-      <c r="Q401" t="n">
-        <v>0</v>
-      </c>
       <c r="R401" t="n">
         <v>0.08711289886137998</v>
       </c>
@@ -71761,9 +71287,6 @@
       <c r="O404" t="n">
         <v>2</v>
       </c>
-      <c r="Q404" t="n">
-        <v>0</v>
-      </c>
       <c r="R404" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -72305,9 +71828,6 @@
       <c r="O407" t="n">
         <v>1</v>
       </c>
-      <c r="Q407" t="n">
-        <v>0</v>
-      </c>
       <c r="R407" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -72453,9 +71973,6 @@
       <c r="O408" t="n">
         <v>3</v>
       </c>
-      <c r="Q408" t="n">
-        <v>0</v>
-      </c>
       <c r="R408" t="n">
         <v>0.06533467414603497</v>
       </c>
@@ -73145,9 +72662,6 @@
       <c r="O412" t="n">
         <v>4</v>
       </c>
-      <c r="Q412" t="n">
-        <v>0</v>
-      </c>
       <c r="R412" t="n">
         <v>0.07650892820937739</v>
       </c>
@@ -73689,9 +73203,6 @@
       <c r="O415" t="n">
         <v>1</v>
       </c>
-      <c r="Q415" t="n">
-        <v>0</v>
-      </c>
       <c r="R415" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -73837,9 +73348,6 @@
       <c r="O416" t="n">
         <v>5</v>
       </c>
-      <c r="Q416" t="n">
-        <v>0</v>
-      </c>
       <c r="R416" t="n">
         <v>0.108891123576725</v>
       </c>
@@ -74381,9 +73889,6 @@
       <c r="O419" t="n">
         <v>4</v>
       </c>
-      <c r="Q419" t="n">
-        <v>0</v>
-      </c>
       <c r="R419" t="n">
         <v>0.07650892820937739</v>
       </c>
@@ -74925,9 +74430,6 @@
       <c r="O422" t="n">
         <v>0</v>
       </c>
-      <c r="Q422" t="n">
-        <v>0</v>
-      </c>
       <c r="R422" t="n">
         <v>0</v>
       </c>
@@ -75073,9 +74575,6 @@
       <c r="O423" t="n">
         <v>2</v>
       </c>
-      <c r="Q423" t="n">
-        <v>0</v>
-      </c>
       <c r="R423" t="n">
         <v>0.04355644943068999</v>
       </c>
@@ -75617,9 +75116,6 @@
       <c r="O426" t="n">
         <v>3</v>
       </c>
-      <c r="Q426" t="n">
-        <v>0</v>
-      </c>
       <c r="R426" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -76161,9 +75657,6 @@
       <c r="O429" t="n">
         <v>0</v>
       </c>
-      <c r="Q429" t="n">
-        <v>0</v>
-      </c>
       <c r="R429" t="n">
         <v>0</v>
       </c>
@@ -76309,9 +75802,6 @@
       <c r="O430" t="n">
         <v>2</v>
       </c>
-      <c r="Q430" t="n">
-        <v>0</v>
-      </c>
       <c r="R430" t="n">
         <v>0.04355644943068999</v>
       </c>
@@ -77001,9 +76491,6 @@
       <c r="O434" t="n">
         <v>3</v>
       </c>
-      <c r="Q434" t="n">
-        <v>0</v>
-      </c>
       <c r="R434" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -77545,9 +77032,6 @@
       <c r="O437" t="n">
         <v>2</v>
       </c>
-      <c r="Q437" t="n">
-        <v>0</v>
-      </c>
       <c r="R437" t="n">
         <v>0.004193129199294409</v>
       </c>
@@ -77692,9 +77176,6 @@
       </c>
       <c r="O438" t="n">
         <v>2</v>
-      </c>
-      <c r="Q438" t="n">
-        <v>0</v>
       </c>
       <c r="R438" t="n">
         <v>0.04355644943068999</v>
